--- a/public/pe_ratio.xlsx
+++ b/public/pe_ratio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ismae\Documents\GitHub\homesite-hns\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571A3F46-89D3-4D66-AD20-9A9AC74A4CEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C3A50D-7451-4DB8-9B4B-74ADD22F203B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,9 +41,6 @@
     <t>Lifetime</t>
   </si>
   <si>
-    <t>Fair _PE</t>
-  </si>
-  <si>
     <t>Floor_PE</t>
   </si>
   <si>
@@ -51,6 +48,9 @@
   </si>
   <si>
     <t>Life_expectancy</t>
+  </si>
+  <si>
+    <t>Fair_PE</t>
   </si>
 </sst>
 </file>
@@ -485,19 +485,19 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>2</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">

--- a/public/pe_ratio.xlsx
+++ b/public/pe_ratio.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ismae\Documents\GitHub\homesite-hns\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2C3A50D-7451-4DB8-9B4B-74ADD22F203B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE11227A-4A2A-4CCA-B572-D3CD049091D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -144,7 +144,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -166,6 +166,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -519,8 +520,8 @@
         <v>10.360000000000001</v>
       </c>
       <c r="F2" s="4">
-        <f>E2/5</f>
-        <v>2.0720000000000001</v>
+        <f t="shared" ref="F2:F6" si="0">E2/3</f>
+        <v>3.4533333333333336</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -534,16 +535,16 @@
         <v>12.25</v>
       </c>
       <c r="D3" s="5">
-        <f t="shared" ref="D3:D66" si="0">C3/B3</f>
+        <f t="shared" ref="D3:D66" si="1">C3/B3</f>
         <v>0.32930107526881719</v>
       </c>
       <c r="E3" s="4">
-        <f t="shared" ref="E3:E66" si="1">B3*0.28</f>
+        <f t="shared" ref="E3:E66" si="2">B3*0.28</f>
         <v>10.416000000000002</v>
       </c>
       <c r="F3" s="4">
-        <f t="shared" ref="F3:F6" si="2">E3/5</f>
-        <v>2.0832000000000006</v>
+        <f t="shared" si="0"/>
+        <v>3.4720000000000009</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -557,16 +558,16 @@
         <v>11.33</v>
       </c>
       <c r="D4" s="5">
+        <f t="shared" si="1"/>
+        <v>0.30213333333333331</v>
+      </c>
+      <c r="E4" s="4">
+        <f t="shared" si="2"/>
+        <v>10.500000000000002</v>
+      </c>
+      <c r="F4" s="4">
         <f t="shared" si="0"/>
-        <v>0.30213333333333331</v>
-      </c>
-      <c r="E4" s="4">
-        <f t="shared" si="1"/>
-        <v>10.500000000000002</v>
-      </c>
-      <c r="F4" s="4">
-        <f t="shared" si="2"/>
-        <v>2.1000000000000005</v>
+        <v>3.5000000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -580,16 +581,16 @@
         <v>11.41</v>
       </c>
       <c r="D5" s="5">
+        <f t="shared" si="1"/>
+        <v>0.30185185185185187</v>
+      </c>
+      <c r="E5" s="4">
+        <f t="shared" si="2"/>
+        <v>10.584</v>
+      </c>
+      <c r="F5" s="4">
         <f t="shared" si="0"/>
-        <v>0.30185185185185187</v>
-      </c>
-      <c r="E5" s="4">
-        <f t="shared" si="1"/>
-        <v>10.584</v>
-      </c>
-      <c r="F5" s="4">
-        <f t="shared" si="2"/>
-        <v>2.1168</v>
+        <v>3.528</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -603,16 +604,16 @@
         <v>11.79</v>
       </c>
       <c r="D6" s="5">
+        <f t="shared" si="1"/>
+        <v>0.3102631578947368</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" si="2"/>
+        <v>10.64</v>
+      </c>
+      <c r="F6" s="4">
         <f t="shared" si="0"/>
-        <v>0.3102631578947368</v>
-      </c>
-      <c r="E6" s="4">
-        <f t="shared" si="1"/>
-        <v>10.64</v>
-      </c>
-      <c r="F6" s="4">
-        <f t="shared" si="2"/>
-        <v>2.1280000000000001</v>
+        <v>3.5466666666666669</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -626,11 +627,11 @@
         <v>9.52</v>
       </c>
       <c r="D7" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.24921465968586384</v>
       </c>
       <c r="E7" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10.696000000000002</v>
       </c>
       <c r="F7" s="4">
@@ -649,11 +650,11 @@
         <v>10.57</v>
       </c>
       <c r="D8" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.27454545454545454</v>
       </c>
       <c r="E8" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10.780000000000001</v>
       </c>
       <c r="F8" s="4">
@@ -672,11 +673,11 @@
         <v>12.87</v>
       </c>
       <c r="D9" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.33170103092783504</v>
       </c>
       <c r="E9" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10.864000000000001</v>
       </c>
       <c r="F9" s="4">
@@ -695,11 +696,11 @@
         <v>14.87</v>
       </c>
       <c r="D10" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.38128205128205128</v>
       </c>
       <c r="E10" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10.920000000000002</v>
       </c>
       <c r="F10" s="4">
@@ -718,15 +719,15 @@
         <v>18.47</v>
       </c>
       <c r="D11" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.47117346938775506</v>
       </c>
       <c r="E11" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>10.976000000000003</v>
       </c>
       <c r="F11" s="4">
-        <f t="shared" si="3"/>
+        <f>E11/3</f>
         <v>3.6586666666666674</v>
       </c>
     </row>
@@ -741,11 +742,11 @@
         <v>15.68</v>
       </c>
       <c r="D12" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.39796954314720812</v>
       </c>
       <c r="E12" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.032</v>
       </c>
       <c r="F12" s="4">
@@ -764,11 +765,11 @@
         <v>15.27</v>
       </c>
       <c r="D13" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.38560606060606056</v>
       </c>
       <c r="E13" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.088000000000001</v>
       </c>
       <c r="F13" s="4">
@@ -787,11 +788,11 @@
         <v>14.43</v>
       </c>
       <c r="D14" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.36256281407035179</v>
       </c>
       <c r="E14" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.144</v>
       </c>
       <c r="F14" s="4">
@@ -810,11 +811,11 @@
         <v>13.13</v>
       </c>
       <c r="D15" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.32825000000000004</v>
       </c>
       <c r="E15" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.200000000000001</v>
       </c>
       <c r="F15" s="4">
@@ -833,11 +834,11 @@
         <v>16.7</v>
       </c>
       <c r="D16" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.41542288557213924</v>
       </c>
       <c r="E16" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.256000000000002</v>
       </c>
       <c r="F16" s="4">
@@ -856,11 +857,11 @@
         <v>17.52</v>
       </c>
       <c r="D17" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.43366336633663366</v>
       </c>
       <c r="E17" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.312000000000001</v>
       </c>
       <c r="F17" s="4">
@@ -879,11 +880,11 @@
         <v>15.36</v>
       </c>
       <c r="D18" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.37832512315270933</v>
       </c>
       <c r="E18" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.368000000000002</v>
       </c>
       <c r="F18" s="4">
@@ -902,11 +903,11 @@
         <v>15.81</v>
       </c>
       <c r="D19" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.38750000000000007</v>
       </c>
       <c r="E19" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.423999999999999</v>
       </c>
       <c r="F19" s="4">
@@ -925,11 +926,11 @@
         <v>17.22</v>
       </c>
       <c r="D20" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.42</v>
       </c>
       <c r="E20" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.48</v>
       </c>
       <c r="F20" s="4">
@@ -948,11 +949,11 @@
         <v>15.43</v>
       </c>
       <c r="D21" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.37180722891566265</v>
       </c>
       <c r="E21" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.620000000000001</v>
       </c>
       <c r="F21" s="4">
@@ -971,11 +972,11 @@
         <v>19.010000000000002</v>
       </c>
       <c r="D22" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.45261904761904764</v>
       </c>
       <c r="E22" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.760000000000002</v>
       </c>
       <c r="F22" s="4">
@@ -994,11 +995,11 @@
         <v>17.649999999999999</v>
       </c>
       <c r="D23" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.41529411764705881</v>
       </c>
       <c r="E23" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.9</v>
       </c>
       <c r="F23" s="4">
@@ -1017,11 +1018,11 @@
         <v>15.74</v>
       </c>
       <c r="D24" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.36604651162790697</v>
       </c>
       <c r="E24" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12.040000000000001</v>
       </c>
       <c r="F24" s="4">
@@ -1040,11 +1041,11 @@
         <v>16.510000000000002</v>
       </c>
       <c r="D25" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.37954022988505753</v>
       </c>
       <c r="E25" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12.180000000000001</v>
       </c>
       <c r="F25" s="4">
@@ -1063,11 +1064,11 @@
         <v>16.579999999999998</v>
       </c>
       <c r="D26" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.37681818181818177</v>
       </c>
       <c r="E26" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12.32</v>
       </c>
       <c r="F26" s="4">
@@ -1086,11 +1087,11 @@
         <v>17.03</v>
       </c>
       <c r="D27" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.38269662921348319</v>
       </c>
       <c r="E27" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12.46</v>
       </c>
       <c r="F27" s="4">
@@ -1109,11 +1110,11 @@
         <v>19.25</v>
       </c>
       <c r="D28" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.42777777777777776</v>
       </c>
       <c r="E28" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12.600000000000001</v>
       </c>
       <c r="F28" s="4">
@@ -1132,11 +1133,11 @@
         <v>22.92</v>
       </c>
       <c r="D29" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.50373626373626379</v>
       </c>
       <c r="E29" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12.740000000000002</v>
       </c>
       <c r="F29" s="4">
@@ -1155,11 +1156,11 @@
         <v>18.670000000000002</v>
       </c>
       <c r="D30" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.40586956521739131</v>
       </c>
       <c r="E30" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12.88</v>
       </c>
       <c r="F30" s="4">
@@ -1178,11 +1179,11 @@
         <v>20.97</v>
       </c>
       <c r="D31" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.45096774193548383</v>
       </c>
       <c r="E31" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13.020000000000001</v>
       </c>
       <c r="F31" s="4">
@@ -1201,11 +1202,11 @@
         <v>22.34</v>
       </c>
       <c r="D32" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.47531914893617022</v>
       </c>
       <c r="E32" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13.160000000000002</v>
       </c>
       <c r="F32" s="4">
@@ -1224,11 +1225,11 @@
         <v>20.32</v>
       </c>
       <c r="D33" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.42778947368421055</v>
       </c>
       <c r="E33" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13.3</v>
       </c>
       <c r="F33" s="4">
@@ -1247,11 +1248,11 @@
         <v>15.86</v>
       </c>
       <c r="D34" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.33041666666666664</v>
       </c>
       <c r="E34" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13.440000000000001</v>
       </c>
       <c r="F34" s="4">
@@ -1270,11 +1271,11 @@
         <v>18.46</v>
       </c>
       <c r="D35" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.38061855670103095</v>
       </c>
       <c r="E35" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13.580000000000002</v>
       </c>
       <c r="F35" s="4">
@@ -1293,11 +1294,11 @@
         <v>20.13</v>
       </c>
       <c r="D36" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.41081632653061223</v>
       </c>
       <c r="E36" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13.72</v>
       </c>
       <c r="F36" s="4">
@@ -1316,11 +1317,11 @@
         <v>17.22</v>
       </c>
       <c r="D37" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.34787878787878784</v>
       </c>
       <c r="E37" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13.860000000000001</v>
       </c>
       <c r="F37" s="4">
@@ -1339,11 +1340,11 @@
         <v>11.9</v>
       </c>
       <c r="D38" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.23800000000000002</v>
       </c>
       <c r="E38" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14.000000000000002</v>
       </c>
       <c r="F38" s="4">
@@ -1362,11 +1363,11 @@
         <v>14.77</v>
       </c>
       <c r="D39" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.29247524752475246</v>
       </c>
       <c r="E39" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14.14</v>
       </c>
       <c r="F39" s="4">
@@ -1385,11 +1386,11 @@
         <v>14.54</v>
       </c>
       <c r="D40" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.28509803921568627</v>
       </c>
       <c r="E40" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14.280000000000001</v>
       </c>
       <c r="F40" s="4">
@@ -1408,11 +1409,11 @@
         <v>14.05</v>
       </c>
       <c r="D41" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.27176015473887816</v>
       </c>
       <c r="E41" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14.476000000000003</v>
       </c>
       <c r="F41" s="4">
@@ -1431,11 +1432,11 @@
         <v>13.8</v>
       </c>
       <c r="D42" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.26386233269598475</v>
       </c>
       <c r="E42" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14.644</v>
       </c>
       <c r="F42" s="4">
@@ -1454,11 +1455,11 @@
         <v>13.15</v>
       </c>
       <c r="D43" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.24811320754716981</v>
       </c>
       <c r="E43" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14.840000000000002</v>
       </c>
       <c r="F43" s="4">
@@ -1477,11 +1478,11 @@
         <v>11.64</v>
       </c>
       <c r="D44" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.22601941747572818</v>
       </c>
       <c r="E44" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14.420000000000002</v>
       </c>
       <c r="F44" s="4">
@@ -1500,11 +1501,11 @@
         <v>10.36</v>
       </c>
       <c r="D45" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.2072</v>
       </c>
       <c r="E45" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>14.000000000000002</v>
       </c>
       <c r="F45" s="4">
@@ -1523,11 +1524,11 @@
         <v>12.54</v>
       </c>
       <c r="D46" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.2685224839400428</v>
       </c>
       <c r="E46" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13.076000000000002</v>
       </c>
       <c r="F46" s="4">
@@ -1546,11 +1547,11 @@
         <v>10.99</v>
       </c>
       <c r="D47" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.25381062355658202</v>
       </c>
       <c r="E47" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>12.124000000000001</v>
       </c>
       <c r="F47" s="4">
@@ -1569,15 +1570,15 @@
         <v>6.64</v>
       </c>
       <c r="D48" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.16599999999999998</v>
       </c>
       <c r="E48" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>11.200000000000001</v>
       </c>
       <c r="F48" s="4">
-        <f t="shared" si="3"/>
+        <f>E48/3</f>
         <v>3.7333333333333338</v>
       </c>
     </row>
@@ -1592,11 +1593,11 @@
         <v>6.1</v>
       </c>
       <c r="D49" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.12978723404255318</v>
       </c>
       <c r="E49" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>13.160000000000002</v>
       </c>
       <c r="F49" s="4">
@@ -1615,11 +1616,11 @@
         <v>5.99</v>
       </c>
       <c r="D50" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.11092592592592593</v>
       </c>
       <c r="E50" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15.120000000000001</v>
       </c>
       <c r="F50" s="4">
@@ -1638,11 +1639,11 @@
         <v>5.12</v>
       </c>
       <c r="D51" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>9.3772893772893773E-2</v>
       </c>
       <c r="E51" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15.288000000000002</v>
       </c>
       <c r="F51" s="4">
@@ -1661,11 +1662,11 @@
         <v>6.29</v>
       </c>
       <c r="D52" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.11394927536231883</v>
       </c>
       <c r="E52" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15.456000000000003</v>
       </c>
       <c r="F52" s="4">
@@ -1684,11 +1685,11 @@
         <v>8.15</v>
       </c>
       <c r="D53" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.14605734767025091</v>
       </c>
       <c r="E53" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15.624000000000001</v>
       </c>
       <c r="F53" s="4">
@@ -1707,11 +1708,11 @@
         <v>8.07</v>
       </c>
       <c r="D54" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.14308510638297872</v>
       </c>
       <c r="E54" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15.792000000000002</v>
       </c>
       <c r="F54" s="4">
@@ -1730,11 +1731,11 @@
         <v>9.69</v>
       </c>
       <c r="D55" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.16999999999999998</v>
       </c>
       <c r="E55" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>15.96</v>
       </c>
       <c r="F55" s="4">
@@ -1753,11 +1754,11 @@
         <v>11.34</v>
       </c>
       <c r="D56" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.19687499999999999</v>
       </c>
       <c r="E56" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16.128000000000004</v>
       </c>
       <c r="F56" s="4">
@@ -1776,11 +1777,11 @@
         <v>13.19</v>
       </c>
       <c r="D57" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.22663230240549825</v>
       </c>
       <c r="E57" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16.296000000000003</v>
       </c>
       <c r="F57" s="4">
@@ -1799,11 +1800,11 @@
         <v>18.809999999999999</v>
       </c>
       <c r="D58" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.31989795918367347</v>
       </c>
       <c r="E58" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16.464000000000002</v>
       </c>
       <c r="F58" s="4">
@@ -1822,11 +1823,11 @@
         <v>27.08</v>
       </c>
       <c r="D59" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.45589225589225585</v>
       </c>
       <c r="E59" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16.632000000000001</v>
       </c>
       <c r="F59" s="4">
@@ -1845,11 +1846,11 @@
         <v>22.31</v>
       </c>
       <c r="D60" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.37183333333333329</v>
       </c>
       <c r="E60" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16.8</v>
       </c>
       <c r="F60" s="4">
@@ -1868,11 +1869,11 @@
         <v>16.71</v>
       </c>
       <c r="D61" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.27757475083056476</v>
       </c>
       <c r="E61" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16.856000000000002</v>
       </c>
       <c r="F61" s="4">
@@ -1891,11 +1892,11 @@
         <v>9.31</v>
       </c>
       <c r="D62" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.15413907284768213</v>
       </c>
       <c r="E62" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16.912000000000003</v>
       </c>
       <c r="F62" s="4">
@@ -1914,11 +1915,11 @@
         <v>8.73</v>
       </c>
       <c r="D63" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.14405940594059408</v>
       </c>
       <c r="E63" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16.968000000000004</v>
       </c>
       <c r="F63" s="4">
@@ -1937,11 +1938,11 @@
         <v>13.03</v>
       </c>
       <c r="D64" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.2143092105263158</v>
       </c>
       <c r="E64" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>17.024000000000001</v>
       </c>
       <c r="F64" s="4">
@@ -1960,11 +1961,11 @@
         <v>11.5</v>
       </c>
       <c r="D65" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.18852459016393441</v>
       </c>
       <c r="E65" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>17.080000000000002</v>
       </c>
       <c r="F65" s="4">
@@ -1983,11 +1984,11 @@
         <v>17.09</v>
       </c>
       <c r="D66" s="5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0.27833876221498371</v>
       </c>
       <c r="E66" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>17.192</v>
       </c>
       <c r="F66" s="4">
@@ -4053,7 +4054,7 @@
         <v>39.65</v>
       </c>
       <c r="D156" s="5">
-        <f t="shared" si="7"/>
+        <f>C156/B156</f>
         <v>0.48353658536585364</v>
       </c>
       <c r="E156" s="4">
@@ -4066,6 +4067,7 @@
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="C157" s="9"/>
       <c r="D157" s="6"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.35">

--- a/public/pe_ratio.xlsx
+++ b/public/pe_ratio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ismae\Documents\GitHub\homesite-hns\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE11227A-4A2A-4CCA-B572-D3CD049091D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB932A2-FC46-4058-A226-EE2DE02CB7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -158,7 +158,6 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -167,6 +166,7 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -494,10 +494,10 @@
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>2</v>
       </c>
     </row>
@@ -511,7 +511,7 @@
       <c r="C2" s="4">
         <v>11.9</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="9">
         <f>C2/B2</f>
         <v>0.32162162162162161</v>
       </c>
@@ -534,7 +534,7 @@
       <c r="C3" s="4">
         <v>12.25</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="9">
         <f t="shared" ref="D3:D66" si="1">C3/B3</f>
         <v>0.32930107526881719</v>
       </c>
@@ -557,7 +557,7 @@
       <c r="C4" s="4">
         <v>11.33</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="9">
         <f t="shared" si="1"/>
         <v>0.30213333333333331</v>
       </c>
@@ -580,7 +580,7 @@
       <c r="C5" s="4">
         <v>11.41</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="9">
         <f t="shared" si="1"/>
         <v>0.30185185185185187</v>
       </c>
@@ -603,7 +603,7 @@
       <c r="C6" s="4">
         <v>11.79</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="9">
         <f t="shared" si="1"/>
         <v>0.3102631578947368</v>
       </c>
@@ -626,7 +626,7 @@
       <c r="C7" s="4">
         <v>9.52</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="9">
         <f t="shared" si="1"/>
         <v>0.24921465968586384</v>
       </c>
@@ -649,7 +649,7 @@
       <c r="C8" s="4">
         <v>10.57</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="9">
         <f t="shared" si="1"/>
         <v>0.27454545454545454</v>
       </c>
@@ -672,7 +672,7 @@
       <c r="C9" s="4">
         <v>12.87</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="9">
         <f t="shared" si="1"/>
         <v>0.33170103092783504</v>
       </c>
@@ -695,7 +695,7 @@
       <c r="C10" s="4">
         <v>14.87</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="9">
         <f t="shared" si="1"/>
         <v>0.38128205128205128</v>
       </c>
@@ -718,7 +718,7 @@
       <c r="C11" s="4">
         <v>18.47</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="9">
         <f t="shared" si="1"/>
         <v>0.47117346938775506</v>
       </c>
@@ -741,7 +741,7 @@
       <c r="C12" s="4">
         <v>15.68</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="9">
         <f t="shared" si="1"/>
         <v>0.39796954314720812</v>
       </c>
@@ -764,7 +764,7 @@
       <c r="C13" s="4">
         <v>15.27</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="9">
         <f t="shared" si="1"/>
         <v>0.38560606060606056</v>
       </c>
@@ -787,7 +787,7 @@
       <c r="C14" s="4">
         <v>14.43</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="9">
         <f t="shared" si="1"/>
         <v>0.36256281407035179</v>
       </c>
@@ -810,7 +810,7 @@
       <c r="C15" s="4">
         <v>13.13</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="9">
         <f t="shared" si="1"/>
         <v>0.32825000000000004</v>
       </c>
@@ -833,7 +833,7 @@
       <c r="C16" s="4">
         <v>16.7</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="9">
         <f t="shared" si="1"/>
         <v>0.41542288557213924</v>
       </c>
@@ -856,7 +856,7 @@
       <c r="C17" s="4">
         <v>17.52</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="9">
         <f t="shared" si="1"/>
         <v>0.43366336633663366</v>
       </c>
@@ -879,7 +879,7 @@
       <c r="C18" s="4">
         <v>15.36</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="9">
         <f t="shared" si="1"/>
         <v>0.37832512315270933</v>
       </c>
@@ -902,7 +902,7 @@
       <c r="C19" s="4">
         <v>15.81</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="9">
         <f t="shared" si="1"/>
         <v>0.38750000000000007</v>
       </c>
@@ -925,7 +925,7 @@
       <c r="C20" s="4">
         <v>17.22</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="9">
         <f t="shared" si="1"/>
         <v>0.42</v>
       </c>
@@ -948,7 +948,7 @@
       <c r="C21" s="4">
         <v>15.43</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="9">
         <f t="shared" si="1"/>
         <v>0.37180722891566265</v>
       </c>
@@ -971,7 +971,7 @@
       <c r="C22" s="4">
         <v>19.010000000000002</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="9">
         <f t="shared" si="1"/>
         <v>0.45261904761904764</v>
       </c>
@@ -994,7 +994,7 @@
       <c r="C23" s="4">
         <v>17.649999999999999</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="9">
         <f t="shared" si="1"/>
         <v>0.41529411764705881</v>
       </c>
@@ -1017,7 +1017,7 @@
       <c r="C24" s="4">
         <v>15.74</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="9">
         <f t="shared" si="1"/>
         <v>0.36604651162790697</v>
       </c>
@@ -1040,7 +1040,7 @@
       <c r="C25" s="4">
         <v>16.510000000000002</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="9">
         <f t="shared" si="1"/>
         <v>0.37954022988505753</v>
       </c>
@@ -1063,7 +1063,7 @@
       <c r="C26" s="4">
         <v>16.579999999999998</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="9">
         <f t="shared" si="1"/>
         <v>0.37681818181818177</v>
       </c>
@@ -1086,7 +1086,7 @@
       <c r="C27" s="4">
         <v>17.03</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="9">
         <f t="shared" si="1"/>
         <v>0.38269662921348319</v>
       </c>
@@ -1109,7 +1109,7 @@
       <c r="C28" s="4">
         <v>19.25</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="9">
         <f t="shared" si="1"/>
         <v>0.42777777777777776</v>
       </c>
@@ -1132,7 +1132,7 @@
       <c r="C29" s="4">
         <v>22.92</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="9">
         <f t="shared" si="1"/>
         <v>0.50373626373626379</v>
       </c>
@@ -1155,7 +1155,7 @@
       <c r="C30" s="4">
         <v>18.670000000000002</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="9">
         <f t="shared" si="1"/>
         <v>0.40586956521739131</v>
       </c>
@@ -1178,7 +1178,7 @@
       <c r="C31" s="4">
         <v>20.97</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="9">
         <f t="shared" si="1"/>
         <v>0.45096774193548383</v>
       </c>
@@ -1201,7 +1201,7 @@
       <c r="C32" s="4">
         <v>22.34</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="9">
         <f t="shared" si="1"/>
         <v>0.47531914893617022</v>
       </c>
@@ -1224,7 +1224,7 @@
       <c r="C33" s="4">
         <v>20.32</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="9">
         <f t="shared" si="1"/>
         <v>0.42778947368421055</v>
       </c>
@@ -1247,7 +1247,7 @@
       <c r="C34" s="4">
         <v>15.86</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="9">
         <f t="shared" si="1"/>
         <v>0.33041666666666664</v>
       </c>
@@ -1270,7 +1270,7 @@
       <c r="C35" s="4">
         <v>18.46</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="9">
         <f t="shared" si="1"/>
         <v>0.38061855670103095</v>
       </c>
@@ -1293,7 +1293,7 @@
       <c r="C36" s="4">
         <v>20.13</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="9">
         <f t="shared" si="1"/>
         <v>0.41081632653061223</v>
       </c>
@@ -1316,7 +1316,7 @@
       <c r="C37" s="4">
         <v>17.22</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="9">
         <f t="shared" si="1"/>
         <v>0.34787878787878784</v>
       </c>
@@ -1339,7 +1339,7 @@
       <c r="C38" s="4">
         <v>11.9</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38" s="9">
         <f t="shared" si="1"/>
         <v>0.23800000000000002</v>
       </c>
@@ -1362,7 +1362,7 @@
       <c r="C39" s="4">
         <v>14.77</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="9">
         <f t="shared" si="1"/>
         <v>0.29247524752475246</v>
       </c>
@@ -1385,7 +1385,7 @@
       <c r="C40" s="4">
         <v>14.54</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="9">
         <f t="shared" si="1"/>
         <v>0.28509803921568627</v>
       </c>
@@ -1408,7 +1408,7 @@
       <c r="C41" s="4">
         <v>14.05</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="9">
         <f t="shared" si="1"/>
         <v>0.27176015473887816</v>
       </c>
@@ -1431,7 +1431,7 @@
       <c r="C42" s="4">
         <v>13.8</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="9">
         <f t="shared" si="1"/>
         <v>0.26386233269598475</v>
       </c>
@@ -1454,7 +1454,7 @@
       <c r="C43" s="4">
         <v>13.15</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="9">
         <f t="shared" si="1"/>
         <v>0.24811320754716981</v>
       </c>
@@ -1477,7 +1477,7 @@
       <c r="C44" s="4">
         <v>11.64</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="9">
         <f t="shared" si="1"/>
         <v>0.22601941747572818</v>
       </c>
@@ -1500,7 +1500,7 @@
       <c r="C45" s="4">
         <v>10.36</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="9">
         <f t="shared" si="1"/>
         <v>0.2072</v>
       </c>
@@ -1523,7 +1523,7 @@
       <c r="C46" s="4">
         <v>12.54</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46" s="9">
         <f t="shared" si="1"/>
         <v>0.2685224839400428</v>
       </c>
@@ -1546,7 +1546,7 @@
       <c r="C47" s="4">
         <v>10.99</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="9">
         <f t="shared" si="1"/>
         <v>0.25381062355658202</v>
       </c>
@@ -1569,7 +1569,7 @@
       <c r="C48" s="4">
         <v>6.64</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="9">
         <f t="shared" si="1"/>
         <v>0.16599999999999998</v>
       </c>
@@ -1592,7 +1592,7 @@
       <c r="C49" s="4">
         <v>6.1</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="9">
         <f t="shared" si="1"/>
         <v>0.12978723404255318</v>
       </c>
@@ -1615,7 +1615,7 @@
       <c r="C50" s="4">
         <v>5.99</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="9">
         <f t="shared" si="1"/>
         <v>0.11092592592592593</v>
       </c>
@@ -1638,7 +1638,7 @@
       <c r="C51" s="4">
         <v>5.12</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51" s="9">
         <f t="shared" si="1"/>
         <v>9.3772893772893773E-2</v>
       </c>
@@ -1661,7 +1661,7 @@
       <c r="C52" s="4">
         <v>6.29</v>
       </c>
-      <c r="D52" s="5">
+      <c r="D52" s="9">
         <f t="shared" si="1"/>
         <v>0.11394927536231883</v>
       </c>
@@ -1684,7 +1684,7 @@
       <c r="C53" s="4">
         <v>8.15</v>
       </c>
-      <c r="D53" s="5">
+      <c r="D53" s="9">
         <f t="shared" si="1"/>
         <v>0.14605734767025091</v>
       </c>
@@ -1707,7 +1707,7 @@
       <c r="C54" s="4">
         <v>8.07</v>
       </c>
-      <c r="D54" s="5">
+      <c r="D54" s="9">
         <f t="shared" si="1"/>
         <v>0.14308510638297872</v>
       </c>
@@ -1730,7 +1730,7 @@
       <c r="C55" s="4">
         <v>9.69</v>
       </c>
-      <c r="D55" s="5">
+      <c r="D55" s="9">
         <f t="shared" si="1"/>
         <v>0.16999999999999998</v>
       </c>
@@ -1753,7 +1753,7 @@
       <c r="C56" s="4">
         <v>11.34</v>
       </c>
-      <c r="D56" s="5">
+      <c r="D56" s="9">
         <f t="shared" si="1"/>
         <v>0.19687499999999999</v>
       </c>
@@ -1776,7 +1776,7 @@
       <c r="C57" s="4">
         <v>13.19</v>
       </c>
-      <c r="D57" s="5">
+      <c r="D57" s="9">
         <f t="shared" si="1"/>
         <v>0.22663230240549825</v>
       </c>
@@ -1799,7 +1799,7 @@
       <c r="C58" s="4">
         <v>18.809999999999999</v>
       </c>
-      <c r="D58" s="5">
+      <c r="D58" s="9">
         <f t="shared" si="1"/>
         <v>0.31989795918367347</v>
       </c>
@@ -1822,7 +1822,7 @@
       <c r="C59" s="4">
         <v>27.08</v>
       </c>
-      <c r="D59" s="5">
+      <c r="D59" s="9">
         <f t="shared" si="1"/>
         <v>0.45589225589225585</v>
       </c>
@@ -1845,7 +1845,7 @@
       <c r="C60" s="4">
         <v>22.31</v>
       </c>
-      <c r="D60" s="5">
+      <c r="D60" s="9">
         <f t="shared" si="1"/>
         <v>0.37183333333333329</v>
       </c>
@@ -1868,7 +1868,7 @@
       <c r="C61" s="4">
         <v>16.71</v>
       </c>
-      <c r="D61" s="5">
+      <c r="D61" s="9">
         <f t="shared" si="1"/>
         <v>0.27757475083056476</v>
       </c>
@@ -1891,7 +1891,7 @@
       <c r="C62" s="4">
         <v>9.31</v>
       </c>
-      <c r="D62" s="5">
+      <c r="D62" s="9">
         <f t="shared" si="1"/>
         <v>0.15413907284768213</v>
       </c>
@@ -1914,7 +1914,7 @@
       <c r="C63" s="4">
         <v>8.73</v>
       </c>
-      <c r="D63" s="5">
+      <c r="D63" s="9">
         <f t="shared" si="1"/>
         <v>0.14405940594059408</v>
       </c>
@@ -1937,7 +1937,7 @@
       <c r="C64" s="4">
         <v>13.03</v>
       </c>
-      <c r="D64" s="5">
+      <c r="D64" s="9">
         <f t="shared" si="1"/>
         <v>0.2143092105263158</v>
       </c>
@@ -1960,7 +1960,7 @@
       <c r="C65" s="4">
         <v>11.5</v>
       </c>
-      <c r="D65" s="5">
+      <c r="D65" s="9">
         <f t="shared" si="1"/>
         <v>0.18852459016393441</v>
       </c>
@@ -1983,7 +1983,7 @@
       <c r="C66" s="4">
         <v>17.09</v>
       </c>
-      <c r="D66" s="5">
+      <c r="D66" s="9">
         <f t="shared" si="1"/>
         <v>0.27833876221498371</v>
       </c>
@@ -2006,7 +2006,7 @@
       <c r="C67" s="4">
         <v>21.62</v>
       </c>
-      <c r="D67" s="5">
+      <c r="D67" s="9">
         <f t="shared" ref="D67:D130" si="4">C67/B67</f>
         <v>0.34983818770226538</v>
       </c>
@@ -2029,7 +2029,7 @@
       <c r="C68" s="4">
         <v>13.51</v>
       </c>
-      <c r="D68" s="5">
+      <c r="D68" s="9">
         <f t="shared" si="4"/>
         <v>0.21720257234726686</v>
       </c>
@@ -2052,7 +2052,7 @@
       <c r="C69" s="4">
         <v>15.6</v>
       </c>
-      <c r="D69" s="5">
+      <c r="D69" s="9">
         <f t="shared" si="4"/>
         <v>0.24920127795527156</v>
       </c>
@@ -2075,7 +2075,7 @@
       <c r="C70" s="4">
         <v>16.38</v>
       </c>
-      <c r="D70" s="5">
+      <c r="D70" s="9">
         <f t="shared" si="4"/>
         <v>0.26</v>
       </c>
@@ -2098,7 +2098,7 @@
       <c r="C71" s="4">
         <v>13.9</v>
       </c>
-      <c r="D71" s="5">
+      <c r="D71" s="9">
         <f t="shared" si="4"/>
         <v>0.2231139646869984</v>
       </c>
@@ -2121,7 +2121,7 @@
       <c r="C72" s="4">
         <v>10.1</v>
       </c>
-      <c r="D72" s="5">
+      <c r="D72" s="9">
         <f t="shared" si="4"/>
         <v>0.16369529983792544</v>
       </c>
@@ -2144,7 +2144,7 @@
       <c r="C73" s="4">
         <v>10.15</v>
       </c>
-      <c r="D73" s="5">
+      <c r="D73" s="9">
         <f t="shared" si="4"/>
         <v>0.16639344262295083</v>
       </c>
@@ -2167,7 +2167,7 @@
       <c r="C74" s="4">
         <v>11.05</v>
       </c>
-      <c r="D74" s="5">
+      <c r="D74" s="9">
         <f t="shared" si="4"/>
         <v>0.17967479674796749</v>
       </c>
@@ -2190,7 +2190,7 @@
       <c r="C75" s="4">
         <v>11.96</v>
       </c>
-      <c r="D75" s="5">
+      <c r="D75" s="9">
         <f t="shared" si="4"/>
         <v>0.19290322580645164</v>
       </c>
@@ -2213,7 +2213,7 @@
       <c r="C76" s="4">
         <v>15.62</v>
       </c>
-      <c r="D76" s="5">
+      <c r="D76" s="9">
         <f t="shared" si="4"/>
         <v>0.24872611464968153</v>
       </c>
@@ -2236,7 +2236,7 @@
       <c r="C77" s="4">
         <v>11.47</v>
       </c>
-      <c r="D77" s="5">
+      <c r="D77" s="9">
         <f t="shared" si="4"/>
         <v>0.18034591194968555</v>
       </c>
@@ -2259,7 +2259,7 @@
       <c r="C78" s="4">
         <v>10.42</v>
       </c>
-      <c r="D78" s="5">
+      <c r="D78" s="9">
         <f t="shared" si="4"/>
         <v>0.16180124223602482</v>
       </c>
@@ -2282,7 +2282,7 @@
       <c r="C79" s="4">
         <v>10.25</v>
       </c>
-      <c r="D79" s="5">
+      <c r="D79" s="9">
         <f t="shared" si="4"/>
         <v>0.1572085889570552</v>
       </c>
@@ -2305,7 +2305,7 @@
       <c r="C80" s="4">
         <v>10.75</v>
       </c>
-      <c r="D80" s="5">
+      <c r="D80" s="9">
         <f t="shared" si="4"/>
         <v>0.16287878787878787</v>
       </c>
@@ -2328,7 +2328,7 @@
       <c r="C81" s="4">
         <v>11.9</v>
       </c>
-      <c r="D81" s="5">
+      <c r="D81" s="9">
         <f t="shared" si="4"/>
         <v>0.1792168674698795</v>
       </c>
@@ -2351,7 +2351,7 @@
       <c r="C82" s="4">
         <v>12.53</v>
       </c>
-      <c r="D82" s="5">
+      <c r="D82" s="9">
         <f t="shared" si="4"/>
         <v>0.18757485029940119</v>
       </c>
@@ -2374,7 +2374,7 @@
       <c r="C83" s="4">
         <v>13.01</v>
       </c>
-      <c r="D83" s="5">
+      <c r="D83" s="9">
         <f t="shared" si="4"/>
         <v>0.19360119047619045</v>
       </c>
@@ -2397,7 +2397,7 @@
       <c r="C84" s="4">
         <v>12</v>
       </c>
-      <c r="D84" s="5">
+      <c r="D84" s="9">
         <f t="shared" si="4"/>
         <v>0.1775147928994083</v>
       </c>
@@ -2420,7 +2420,7 @@
       <c r="C85" s="4">
         <v>15.99</v>
       </c>
-      <c r="D85" s="5">
+      <c r="D85" s="9">
         <f t="shared" si="4"/>
         <v>0.2351470588235294</v>
       </c>
@@ -2443,7 +2443,7 @@
       <c r="C86" s="4">
         <v>18.29</v>
       </c>
-      <c r="D86" s="5">
+      <c r="D86" s="9">
         <f t="shared" si="4"/>
         <v>0.26739766081871341</v>
       </c>
@@ -2466,7 +2466,7 @@
       <c r="C87" s="4">
         <v>16.72</v>
       </c>
-      <c r="D87" s="5">
+      <c r="D87" s="9">
         <f t="shared" si="4"/>
         <v>0.24302325581395348</v>
       </c>
@@ -2489,7 +2489,7 @@
       <c r="C88" s="4">
         <v>13.79</v>
       </c>
-      <c r="D88" s="5">
+      <c r="D88" s="9">
         <f t="shared" si="4"/>
         <v>0.19927745664739882</v>
       </c>
@@ -2512,7 +2512,7 @@
       <c r="C89" s="4">
         <v>17.98</v>
       </c>
-      <c r="D89" s="5">
+      <c r="D89" s="9">
         <f t="shared" si="4"/>
         <v>0.25833333333333336</v>
       </c>
@@ -2535,7 +2535,7 @@
       <c r="C90" s="4">
         <v>18.34</v>
       </c>
-      <c r="D90" s="5">
+      <c r="D90" s="9">
         <f t="shared" si="4"/>
         <v>0.26200000000000001</v>
       </c>
@@ -2558,7 +2558,7 @@
       <c r="C91" s="4">
         <v>18.47</v>
       </c>
-      <c r="D91" s="5">
+      <c r="D91" s="9">
         <f t="shared" si="4"/>
         <v>0.26310541310541308</v>
       </c>
@@ -2581,7 +2581,7 @@
       <c r="C92" s="4">
         <v>21.2</v>
       </c>
-      <c r="D92" s="5">
+      <c r="D92" s="9">
         <f t="shared" si="4"/>
         <v>0.30113636363636359</v>
       </c>
@@ -2604,7 +2604,7 @@
       <c r="C93" s="4">
         <v>19.260000000000002</v>
       </c>
-      <c r="D93" s="5">
+      <c r="D93" s="9">
         <f t="shared" si="4"/>
         <v>0.27280453257790371</v>
       </c>
@@ -2627,7 +2627,7 @@
       <c r="C94" s="4">
         <v>21.63</v>
       </c>
-      <c r="D94" s="5">
+      <c r="D94" s="9">
         <f t="shared" si="4"/>
         <v>0.30550847457627117</v>
       </c>
@@ -2650,7 +2650,7 @@
       <c r="C95" s="4">
         <v>23.27</v>
       </c>
-      <c r="D95" s="5">
+      <c r="D95" s="9">
         <f t="shared" si="4"/>
         <v>0.32774647887323943</v>
       </c>
@@ -2673,7 +2673,7 @@
       <c r="C96" s="4">
         <v>24.06</v>
       </c>
-      <c r="D96" s="5">
+      <c r="D96" s="9">
         <f t="shared" si="4"/>
         <v>0.33839662447257385</v>
       </c>
@@ -2696,7 +2696,7 @@
       <c r="C97" s="4">
         <v>20.43</v>
       </c>
-      <c r="D97" s="5">
+      <c r="D97" s="9">
         <f t="shared" si="4"/>
         <v>0.28693820224719102</v>
       </c>
@@ -2719,7 +2719,7 @@
       <c r="C98" s="4">
         <v>21.51</v>
       </c>
-      <c r="D98" s="5">
+      <c r="D98" s="9">
         <f t="shared" si="4"/>
         <v>0.30168302945301545</v>
       </c>
@@ -2742,7 +2742,7 @@
       <c r="C99" s="4">
         <v>21.19</v>
       </c>
-      <c r="D99" s="5">
+      <c r="D99" s="9">
         <f t="shared" si="4"/>
         <v>0.29677871148459384</v>
       </c>
@@ -2765,7 +2765,7 @@
       <c r="C100" s="4">
         <v>17.09</v>
       </c>
-      <c r="D100" s="5">
+      <c r="D100" s="9">
         <f t="shared" si="4"/>
         <v>0.23902097902097902</v>
       </c>
@@ -2788,7 +2788,7 @@
       <c r="C101" s="4">
         <v>16.46</v>
       </c>
-      <c r="D101" s="5">
+      <c r="D101" s="9">
         <f t="shared" si="4"/>
         <v>0.2295676429567643</v>
       </c>
@@ -2811,7 +2811,7 @@
       <c r="C102" s="4">
         <v>17.260000000000002</v>
       </c>
-      <c r="D102" s="5">
+      <c r="D102" s="9">
         <f t="shared" si="4"/>
         <v>0.24005563282336578</v>
       </c>
@@ -2834,7 +2834,7 @@
       <c r="C103" s="4">
         <v>18.71</v>
       </c>
-      <c r="D103" s="5">
+      <c r="D103" s="9">
         <f t="shared" si="4"/>
         <v>0.25950069348127602</v>
       </c>
@@ -2857,7 +2857,7 @@
       <c r="C104" s="4">
         <v>13.53</v>
       </c>
-      <c r="D104" s="5">
+      <c r="D104" s="9">
         <f t="shared" si="4"/>
         <v>0.18713692946058091</v>
       </c>
@@ -2880,7 +2880,7 @@
       <c r="C105" s="4">
         <v>8.92</v>
       </c>
-      <c r="D105" s="5">
+      <c r="D105" s="9">
         <f t="shared" si="4"/>
         <v>0.12303448275862069</v>
       </c>
@@ -2903,7 +2903,7 @@
       <c r="C106" s="4">
         <v>11.19</v>
       </c>
-      <c r="D106" s="5">
+      <c r="D106" s="9">
         <f t="shared" si="4"/>
         <v>0.15370879120879122</v>
       </c>
@@ -2926,7 +2926,7 @@
       <c r="C107" s="4">
         <v>11.44</v>
       </c>
-      <c r="D107" s="5">
+      <c r="D107" s="9">
         <f t="shared" si="4"/>
         <v>0.15649794801641587</v>
       </c>
@@ -2949,7 +2949,7 @@
       <c r="C108" s="4">
         <v>9.24</v>
       </c>
-      <c r="D108" s="5">
+      <c r="D108" s="9">
         <f t="shared" si="4"/>
         <v>0.12588555858310627</v>
       </c>
@@ -2972,7 +2972,7 @@
       <c r="C109" s="4">
         <v>9.26</v>
       </c>
-      <c r="D109" s="5">
+      <c r="D109" s="9">
         <f t="shared" si="4"/>
         <v>0.12564450474898237</v>
       </c>
@@ -2995,7 +2995,7 @@
       <c r="C110" s="4">
         <v>8.85</v>
       </c>
-      <c r="D110" s="5">
+      <c r="D110" s="9">
         <f t="shared" si="4"/>
         <v>0.11959459459459459</v>
       </c>
@@ -3018,7 +3018,7 @@
       <c r="C111" s="4">
         <v>9.26</v>
       </c>
-      <c r="D111" s="5">
+      <c r="D111" s="9">
         <f t="shared" si="4"/>
         <v>0.12479784366576818</v>
       </c>
@@ -3041,7 +3041,7 @@
       <c r="C112" s="4">
         <v>7.39</v>
       </c>
-      <c r="D112" s="5">
+      <c r="D112" s="9">
         <f t="shared" si="4"/>
         <v>9.9327956989247304E-2</v>
       </c>
@@ -3064,7 +3064,7 @@
       <c r="C113" s="4">
         <v>8.76</v>
       </c>
-      <c r="D113" s="5">
+      <c r="D113" s="9">
         <f t="shared" si="4"/>
         <v>0.11742627345844504</v>
       </c>
@@ -3087,7 +3087,7 @@
       <c r="C114" s="4">
         <v>9.89</v>
       </c>
-      <c r="D114" s="5">
+      <c r="D114" s="9">
         <f t="shared" si="4"/>
         <v>0.13221925133689841</v>
       </c>
@@ -3110,7 +3110,7 @@
       <c r="C115" s="4">
         <v>10</v>
       </c>
-      <c r="D115" s="5">
+      <c r="D115" s="9">
         <f t="shared" si="4"/>
         <v>0.13333333333333333</v>
       </c>
@@ -3133,7 +3133,7 @@
       <c r="C116" s="4">
         <v>11.72</v>
       </c>
-      <c r="D116" s="5">
+      <c r="D116" s="9">
         <f t="shared" si="4"/>
         <v>0.15585106382978722</v>
       </c>
@@ -3156,7 +3156,7 @@
       <c r="C117" s="4">
         <v>14.92</v>
       </c>
-      <c r="D117" s="5">
+      <c r="D117" s="9">
         <f t="shared" si="4"/>
         <v>0.19787798408488061</v>
       </c>
@@ -3179,7 +3179,7 @@
       <c r="C118" s="4">
         <v>13.9</v>
       </c>
-      <c r="D118" s="5">
+      <c r="D118" s="9">
         <f t="shared" si="4"/>
         <v>0.18386243386243389</v>
       </c>
@@ -3202,7 +3202,7 @@
       <c r="C119" s="4">
         <v>15.09</v>
       </c>
-      <c r="D119" s="5">
+      <c r="D119" s="9">
         <f t="shared" si="4"/>
         <v>0.19907651715039579</v>
       </c>
@@ -3225,7 +3225,7 @@
       <c r="C120" s="4">
         <v>17.05</v>
       </c>
-      <c r="D120" s="5">
+      <c r="D120" s="9">
         <f t="shared" si="4"/>
         <v>0.2243421052631579</v>
       </c>
@@ -3248,7 +3248,7 @@
       <c r="C121" s="4">
         <v>15.61</v>
       </c>
-      <c r="D121" s="5">
+      <c r="D121" s="9">
         <f t="shared" si="4"/>
         <v>0.2048556430446194</v>
       </c>
@@ -3271,7 +3271,7 @@
       <c r="C122" s="4">
         <v>19.77</v>
       </c>
-      <c r="D122" s="5">
+      <c r="D122" s="9">
         <f t="shared" si="4"/>
         <v>0.25876963350785337</v>
       </c>
@@ -3294,7 +3294,7 @@
       <c r="C123" s="4">
         <v>20.32</v>
       </c>
-      <c r="D123" s="5">
+      <c r="D123" s="9">
         <f t="shared" si="4"/>
         <v>0.26527415143603134</v>
       </c>
@@ -3317,7 +3317,7 @@
       <c r="C124" s="4">
         <v>21.41</v>
       </c>
-      <c r="D124" s="5">
+      <c r="D124" s="9">
         <f t="shared" si="4"/>
         <v>0.2787760416666667</v>
       </c>
@@ -3340,7 +3340,7 @@
       <c r="C125" s="4">
         <v>20.22</v>
       </c>
-      <c r="D125" s="5">
+      <c r="D125" s="9">
         <f t="shared" si="4"/>
         <v>0.26259740259740261</v>
       </c>
@@ -3363,7 +3363,7 @@
       <c r="C126" s="4">
         <v>24.76</v>
       </c>
-      <c r="D126" s="5">
+      <c r="D126" s="9">
         <f t="shared" si="4"/>
         <v>0.32072538860103628</v>
       </c>
@@ -3386,7 +3386,7 @@
       <c r="C127" s="4">
         <v>28.33</v>
       </c>
-      <c r="D127" s="5">
+      <c r="D127" s="9">
         <f t="shared" si="4"/>
         <v>0.36602067183462528</v>
       </c>
@@ -3409,7 +3409,7 @@
       <c r="C128" s="4">
         <v>32.86</v>
       </c>
-      <c r="D128" s="5">
+      <c r="D128" s="9">
         <f t="shared" si="4"/>
         <v>0.42345360824742273</v>
       </c>
@@ -3432,7 +3432,7 @@
       <c r="C129" s="4">
         <v>40.57</v>
       </c>
-      <c r="D129" s="5">
+      <c r="D129" s="9">
         <f t="shared" si="4"/>
         <v>0.52146529562982002</v>
       </c>
@@ -3455,7 +3455,7 @@
       <c r="C130" s="4">
         <v>43.77</v>
       </c>
-      <c r="D130" s="5">
+      <c r="D130" s="9">
         <f t="shared" si="4"/>
         <v>0.56115384615384623</v>
       </c>
@@ -3478,8 +3478,8 @@
       <c r="C131" s="4">
         <v>36.979999999999997</v>
       </c>
-      <c r="D131" s="5">
-        <f t="shared" ref="D131:D156" si="7">C131/B131</f>
+      <c r="D131" s="9">
+        <f t="shared" ref="D131:D155" si="7">C131/B131</f>
         <v>0.47289002557544751</v>
       </c>
       <c r="E131" s="4">
@@ -3501,7 +3501,7 @@
       <c r="C132" s="4">
         <v>30.28</v>
       </c>
-      <c r="D132" s="5">
+      <c r="D132" s="9">
         <f t="shared" si="7"/>
         <v>0.38622448979591834</v>
       </c>
@@ -3524,7 +3524,7 @@
       <c r="C133" s="4">
         <v>22.9</v>
       </c>
-      <c r="D133" s="5">
+      <c r="D133" s="9">
         <f t="shared" si="7"/>
         <v>0.29134860050890588</v>
       </c>
@@ -3547,7 +3547,7 @@
       <c r="C134" s="4">
         <v>27.66</v>
       </c>
-      <c r="D134" s="5">
+      <c r="D134" s="9">
         <f t="shared" si="7"/>
         <v>0.35101522842639593</v>
       </c>
@@ -3570,7 +3570,7 @@
       <c r="C135" s="4">
         <v>26.59</v>
       </c>
-      <c r="D135" s="5">
+      <c r="D135" s="9">
         <f t="shared" si="7"/>
         <v>0.33658227848101263</v>
       </c>
@@ -3593,7 +3593,7 @@
       <c r="C136" s="4">
         <v>26.47</v>
       </c>
-      <c r="D136" s="5">
+      <c r="D136" s="9">
         <f t="shared" si="7"/>
         <v>0.33421717171717169</v>
       </c>
@@ -3616,7 +3616,7 @@
       <c r="C137" s="4">
         <v>27.21</v>
       </c>
-      <c r="D137" s="5">
+      <c r="D137" s="9">
         <f t="shared" si="7"/>
         <v>0.34269521410579346</v>
       </c>
@@ -3639,7 +3639,7 @@
       <c r="C138" s="4">
         <v>24.02</v>
       </c>
-      <c r="D138" s="5">
+      <c r="D138" s="9">
         <f t="shared" si="7"/>
         <v>0.30175879396984928</v>
       </c>
@@ -3662,7 +3662,7 @@
       <c r="C139" s="4">
         <v>15.17</v>
       </c>
-      <c r="D139" s="5">
+      <c r="D139" s="9">
         <f t="shared" si="7"/>
         <v>0.19010025062656641</v>
       </c>
@@ -3685,7 +3685,7 @@
       <c r="C140" s="4">
         <v>20.53</v>
       </c>
-      <c r="D140" s="5">
+      <c r="D140" s="9">
         <f t="shared" si="7"/>
         <v>0.25662499999999999</v>
       </c>
@@ -3708,7 +3708,7 @@
       <c r="C141" s="4">
         <v>22.98</v>
       </c>
-      <c r="D141" s="5">
+      <c r="D141" s="9">
         <f t="shared" si="7"/>
         <v>0.28653366583541146</v>
       </c>
@@ -3731,7 +3731,7 @@
       <c r="C142" s="4">
         <v>21.21</v>
       </c>
-      <c r="D142" s="5">
+      <c r="D142" s="9">
         <f t="shared" si="7"/>
         <v>0.264134495641345</v>
       </c>
@@ -3754,7 +3754,7 @@
       <c r="C143" s="4">
         <v>21.9</v>
       </c>
-      <c r="D143" s="5">
+      <c r="D143" s="9">
         <f t="shared" si="7"/>
         <v>0.27204968944099378</v>
       </c>
@@ -3777,7 +3777,7 @@
       <c r="C144" s="4">
         <v>24.86</v>
       </c>
-      <c r="D144" s="5">
+      <c r="D144" s="9">
         <f t="shared" si="7"/>
         <v>0.30843672456575683</v>
       </c>
@@ -3800,7 +3800,7 @@
       <c r="C145" s="4">
         <v>26.49</v>
       </c>
-      <c r="D145" s="5">
+      <c r="D145" s="9">
         <f t="shared" si="7"/>
         <v>0.32784653465346536</v>
       </c>
@@ -3823,7 +3823,7 @@
       <c r="C146" s="4">
         <v>24.21</v>
       </c>
-      <c r="D146" s="5">
+      <c r="D146" s="9">
         <f t="shared" si="7"/>
         <v>0.29888888888888893</v>
       </c>
@@ -3846,7 +3846,7 @@
       <c r="C147" s="4">
         <v>28.06</v>
       </c>
-      <c r="D147" s="5">
+      <c r="D147" s="9">
         <f t="shared" si="7"/>
         <v>0.34556650246305415</v>
       </c>
@@ -3869,7 +3869,7 @@
       <c r="C148" s="4">
         <v>33.31</v>
       </c>
-      <c r="D148" s="5">
+      <c r="D148" s="9">
         <f t="shared" si="7"/>
         <v>0.40971709717097177</v>
       </c>
@@ -3892,7 +3892,7 @@
       <c r="C149" s="4">
         <v>28.38</v>
       </c>
-      <c r="D149" s="5">
+      <c r="D149" s="9">
         <f t="shared" si="7"/>
         <v>0.34822085889570553</v>
       </c>
@@ -3915,7 +3915,7 @@
       <c r="C150" s="4">
         <v>30.99</v>
       </c>
-      <c r="D150" s="5">
+      <c r="D150" s="9">
         <f t="shared" si="7"/>
         <v>0.38353960396039605</v>
       </c>
@@ -3938,7 +3938,7 @@
       <c r="C151" s="4">
         <v>34.51</v>
       </c>
-      <c r="D151" s="5">
+      <c r="D151" s="9">
         <f t="shared" si="7"/>
         <v>0.42976338729763386</v>
       </c>
@@ -3961,7 +3961,7 @@
       <c r="C152" s="4">
         <v>36.94</v>
       </c>
-      <c r="D152" s="5">
+      <c r="D152" s="9">
         <f t="shared" si="7"/>
         <v>0.45717821782178214</v>
       </c>
@@ -3984,7 +3984,7 @@
       <c r="C153" s="4">
         <v>28.34</v>
       </c>
-      <c r="D153" s="5">
+      <c r="D153" s="9">
         <f t="shared" si="7"/>
         <v>0.34858548585485855</v>
       </c>
@@ -4007,7 +4007,7 @@
       <c r="C154" s="4">
         <v>31.97</v>
       </c>
-      <c r="D154" s="5">
+      <c r="D154" s="9">
         <f t="shared" si="7"/>
         <v>0.39178921568627451</v>
       </c>
@@ -4030,7 +4030,7 @@
       <c r="C155" s="4">
         <v>37.14</v>
       </c>
-      <c r="D155" s="5">
+      <c r="D155" s="9">
         <f t="shared" si="7"/>
         <v>0.45403422982885089</v>
       </c>
@@ -4053,7 +4053,7 @@
       <c r="C156" s="4">
         <v>39.65</v>
       </c>
-      <c r="D156" s="5">
+      <c r="D156" s="9">
         <f>C156/B156</f>
         <v>0.48353658536585364</v>
       </c>
@@ -4067,11 +4067,11 @@
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C157" s="9"/>
-      <c r="D157" s="6"/>
+      <c r="C157" s="8"/>
+      <c r="D157" s="5"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A158" s="8"/>
+      <c r="A158" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/public/pe_ratio.xlsx
+++ b/public/pe_ratio.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ismae\Documents\GitHub\homesite-hns\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB932A2-FC46-4058-A226-EE2DE02CB7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74489500-D2EC-4F42-AEC1-12C77DB46EE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -76,12 +76,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color rgb="FF666666"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -142,9 +136,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -158,14 +152,9 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -470,7 +459,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F158"/>
+  <dimension ref="A1:F156"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -494,10 +483,10 @@
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
@@ -511,7 +500,7 @@
       <c r="C2" s="4">
         <v>11.9</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="6">
         <f>C2/B2</f>
         <v>0.32162162162162161</v>
       </c>
@@ -534,7 +523,7 @@
       <c r="C3" s="4">
         <v>12.25</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="6">
         <f t="shared" ref="D3:D66" si="1">C3/B3</f>
         <v>0.32930107526881719</v>
       </c>
@@ -557,7 +546,7 @@
       <c r="C4" s="4">
         <v>11.33</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="6">
         <f t="shared" si="1"/>
         <v>0.30213333333333331</v>
       </c>
@@ -580,7 +569,7 @@
       <c r="C5" s="4">
         <v>11.41</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="6">
         <f t="shared" si="1"/>
         <v>0.30185185185185187</v>
       </c>
@@ -603,7 +592,7 @@
       <c r="C6" s="4">
         <v>11.79</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="6">
         <f t="shared" si="1"/>
         <v>0.3102631578947368</v>
       </c>
@@ -626,7 +615,7 @@
       <c r="C7" s="4">
         <v>9.52</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="6">
         <f t="shared" si="1"/>
         <v>0.24921465968586384</v>
       </c>
@@ -649,7 +638,7 @@
       <c r="C8" s="4">
         <v>10.57</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="6">
         <f t="shared" si="1"/>
         <v>0.27454545454545454</v>
       </c>
@@ -672,7 +661,7 @@
       <c r="C9" s="4">
         <v>12.87</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D9" s="6">
         <f t="shared" si="1"/>
         <v>0.33170103092783504</v>
       </c>
@@ -695,7 +684,7 @@
       <c r="C10" s="4">
         <v>14.87</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="6">
         <f t="shared" si="1"/>
         <v>0.38128205128205128</v>
       </c>
@@ -718,7 +707,7 @@
       <c r="C11" s="4">
         <v>18.47</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D11" s="6">
         <f t="shared" si="1"/>
         <v>0.47117346938775506</v>
       </c>
@@ -741,7 +730,7 @@
       <c r="C12" s="4">
         <v>15.68</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="6">
         <f t="shared" si="1"/>
         <v>0.39796954314720812</v>
       </c>
@@ -764,7 +753,7 @@
       <c r="C13" s="4">
         <v>15.27</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D13" s="6">
         <f t="shared" si="1"/>
         <v>0.38560606060606056</v>
       </c>
@@ -787,7 +776,7 @@
       <c r="C14" s="4">
         <v>14.43</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="6">
         <f t="shared" si="1"/>
         <v>0.36256281407035179</v>
       </c>
@@ -810,7 +799,7 @@
       <c r="C15" s="4">
         <v>13.13</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D15" s="6">
         <f t="shared" si="1"/>
         <v>0.32825000000000004</v>
       </c>
@@ -833,7 +822,7 @@
       <c r="C16" s="4">
         <v>16.7</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="6">
         <f t="shared" si="1"/>
         <v>0.41542288557213924</v>
       </c>
@@ -856,7 +845,7 @@
       <c r="C17" s="4">
         <v>17.52</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="6">
         <f t="shared" si="1"/>
         <v>0.43366336633663366</v>
       </c>
@@ -879,7 +868,7 @@
       <c r="C18" s="4">
         <v>15.36</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="6">
         <f t="shared" si="1"/>
         <v>0.37832512315270933</v>
       </c>
@@ -902,7 +891,7 @@
       <c r="C19" s="4">
         <v>15.81</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="6">
         <f t="shared" si="1"/>
         <v>0.38750000000000007</v>
       </c>
@@ -925,7 +914,7 @@
       <c r="C20" s="4">
         <v>17.22</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="6">
         <f t="shared" si="1"/>
         <v>0.42</v>
       </c>
@@ -948,7 +937,7 @@
       <c r="C21" s="4">
         <v>15.43</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="6">
         <f t="shared" si="1"/>
         <v>0.37180722891566265</v>
       </c>
@@ -971,7 +960,7 @@
       <c r="C22" s="4">
         <v>19.010000000000002</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="6">
         <f t="shared" si="1"/>
         <v>0.45261904761904764</v>
       </c>
@@ -994,7 +983,7 @@
       <c r="C23" s="4">
         <v>17.649999999999999</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="6">
         <f t="shared" si="1"/>
         <v>0.41529411764705881</v>
       </c>
@@ -1017,7 +1006,7 @@
       <c r="C24" s="4">
         <v>15.74</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="6">
         <f t="shared" si="1"/>
         <v>0.36604651162790697</v>
       </c>
@@ -1040,7 +1029,7 @@
       <c r="C25" s="4">
         <v>16.510000000000002</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="6">
         <f t="shared" si="1"/>
         <v>0.37954022988505753</v>
       </c>
@@ -1063,7 +1052,7 @@
       <c r="C26" s="4">
         <v>16.579999999999998</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="6">
         <f t="shared" si="1"/>
         <v>0.37681818181818177</v>
       </c>
@@ -1086,7 +1075,7 @@
       <c r="C27" s="4">
         <v>17.03</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="6">
         <f t="shared" si="1"/>
         <v>0.38269662921348319</v>
       </c>
@@ -1109,7 +1098,7 @@
       <c r="C28" s="4">
         <v>19.25</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="6">
         <f t="shared" si="1"/>
         <v>0.42777777777777776</v>
       </c>
@@ -1132,7 +1121,7 @@
       <c r="C29" s="4">
         <v>22.92</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="6">
         <f t="shared" si="1"/>
         <v>0.50373626373626379</v>
       </c>
@@ -1155,7 +1144,7 @@
       <c r="C30" s="4">
         <v>18.670000000000002</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="6">
         <f t="shared" si="1"/>
         <v>0.40586956521739131</v>
       </c>
@@ -1178,7 +1167,7 @@
       <c r="C31" s="4">
         <v>20.97</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="6">
         <f t="shared" si="1"/>
         <v>0.45096774193548383</v>
       </c>
@@ -1201,7 +1190,7 @@
       <c r="C32" s="4">
         <v>22.34</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="6">
         <f t="shared" si="1"/>
         <v>0.47531914893617022</v>
       </c>
@@ -1224,7 +1213,7 @@
       <c r="C33" s="4">
         <v>20.32</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="6">
         <f t="shared" si="1"/>
         <v>0.42778947368421055</v>
       </c>
@@ -1247,7 +1236,7 @@
       <c r="C34" s="4">
         <v>15.86</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="6">
         <f t="shared" si="1"/>
         <v>0.33041666666666664</v>
       </c>
@@ -1270,7 +1259,7 @@
       <c r="C35" s="4">
         <v>18.46</v>
       </c>
-      <c r="D35" s="9">
+      <c r="D35" s="6">
         <f t="shared" si="1"/>
         <v>0.38061855670103095</v>
       </c>
@@ -1293,7 +1282,7 @@
       <c r="C36" s="4">
         <v>20.13</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="6">
         <f t="shared" si="1"/>
         <v>0.41081632653061223</v>
       </c>
@@ -1316,7 +1305,7 @@
       <c r="C37" s="4">
         <v>17.22</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="6">
         <f t="shared" si="1"/>
         <v>0.34787878787878784</v>
       </c>
@@ -1339,7 +1328,7 @@
       <c r="C38" s="4">
         <v>11.9</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="6">
         <f t="shared" si="1"/>
         <v>0.23800000000000002</v>
       </c>
@@ -1362,7 +1351,7 @@
       <c r="C39" s="4">
         <v>14.77</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="6">
         <f t="shared" si="1"/>
         <v>0.29247524752475246</v>
       </c>
@@ -1385,7 +1374,7 @@
       <c r="C40" s="4">
         <v>14.54</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="6">
         <f t="shared" si="1"/>
         <v>0.28509803921568627</v>
       </c>
@@ -1408,7 +1397,7 @@
       <c r="C41" s="4">
         <v>14.05</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="6">
         <f t="shared" si="1"/>
         <v>0.27176015473887816</v>
       </c>
@@ -1431,7 +1420,7 @@
       <c r="C42" s="4">
         <v>13.8</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="6">
         <f t="shared" si="1"/>
         <v>0.26386233269598475</v>
       </c>
@@ -1454,7 +1443,7 @@
       <c r="C43" s="4">
         <v>13.15</v>
       </c>
-      <c r="D43" s="9">
+      <c r="D43" s="6">
         <f t="shared" si="1"/>
         <v>0.24811320754716981</v>
       </c>
@@ -1477,7 +1466,7 @@
       <c r="C44" s="4">
         <v>11.64</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="6">
         <f t="shared" si="1"/>
         <v>0.22601941747572818</v>
       </c>
@@ -1500,7 +1489,7 @@
       <c r="C45" s="4">
         <v>10.36</v>
       </c>
-      <c r="D45" s="9">
+      <c r="D45" s="6">
         <f t="shared" si="1"/>
         <v>0.2072</v>
       </c>
@@ -1523,7 +1512,7 @@
       <c r="C46" s="4">
         <v>12.54</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="6">
         <f t="shared" si="1"/>
         <v>0.2685224839400428</v>
       </c>
@@ -1546,7 +1535,7 @@
       <c r="C47" s="4">
         <v>10.99</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="6">
         <f t="shared" si="1"/>
         <v>0.25381062355658202</v>
       </c>
@@ -1569,7 +1558,7 @@
       <c r="C48" s="4">
         <v>6.64</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="6">
         <f t="shared" si="1"/>
         <v>0.16599999999999998</v>
       </c>
@@ -1592,7 +1581,7 @@
       <c r="C49" s="4">
         <v>6.1</v>
       </c>
-      <c r="D49" s="9">
+      <c r="D49" s="6">
         <f t="shared" si="1"/>
         <v>0.12978723404255318</v>
       </c>
@@ -1615,7 +1604,7 @@
       <c r="C50" s="4">
         <v>5.99</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="6">
         <f t="shared" si="1"/>
         <v>0.11092592592592593</v>
       </c>
@@ -1638,7 +1627,7 @@
       <c r="C51" s="4">
         <v>5.12</v>
       </c>
-      <c r="D51" s="9">
+      <c r="D51" s="6">
         <f t="shared" si="1"/>
         <v>9.3772893772893773E-2</v>
       </c>
@@ -1661,7 +1650,7 @@
       <c r="C52" s="4">
         <v>6.29</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="6">
         <f t="shared" si="1"/>
         <v>0.11394927536231883</v>
       </c>
@@ -1684,7 +1673,7 @@
       <c r="C53" s="4">
         <v>8.15</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D53" s="6">
         <f t="shared" si="1"/>
         <v>0.14605734767025091</v>
       </c>
@@ -1707,7 +1696,7 @@
       <c r="C54" s="4">
         <v>8.07</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D54" s="6">
         <f t="shared" si="1"/>
         <v>0.14308510638297872</v>
       </c>
@@ -1730,7 +1719,7 @@
       <c r="C55" s="4">
         <v>9.69</v>
       </c>
-      <c r="D55" s="9">
+      <c r="D55" s="6">
         <f t="shared" si="1"/>
         <v>0.16999999999999998</v>
       </c>
@@ -1753,7 +1742,7 @@
       <c r="C56" s="4">
         <v>11.34</v>
       </c>
-      <c r="D56" s="9">
+      <c r="D56" s="6">
         <f t="shared" si="1"/>
         <v>0.19687499999999999</v>
       </c>
@@ -1776,7 +1765,7 @@
       <c r="C57" s="4">
         <v>13.19</v>
       </c>
-      <c r="D57" s="9">
+      <c r="D57" s="6">
         <f t="shared" si="1"/>
         <v>0.22663230240549825</v>
       </c>
@@ -1799,7 +1788,7 @@
       <c r="C58" s="4">
         <v>18.809999999999999</v>
       </c>
-      <c r="D58" s="9">
+      <c r="D58" s="6">
         <f t="shared" si="1"/>
         <v>0.31989795918367347</v>
       </c>
@@ -1822,7 +1811,7 @@
       <c r="C59" s="4">
         <v>27.08</v>
       </c>
-      <c r="D59" s="9">
+      <c r="D59" s="6">
         <f t="shared" si="1"/>
         <v>0.45589225589225585</v>
       </c>
@@ -1845,7 +1834,7 @@
       <c r="C60" s="4">
         <v>22.31</v>
       </c>
-      <c r="D60" s="9">
+      <c r="D60" s="6">
         <f t="shared" si="1"/>
         <v>0.37183333333333329</v>
       </c>
@@ -1868,7 +1857,7 @@
       <c r="C61" s="4">
         <v>16.71</v>
       </c>
-      <c r="D61" s="9">
+      <c r="D61" s="6">
         <f t="shared" si="1"/>
         <v>0.27757475083056476</v>
       </c>
@@ -1891,7 +1880,7 @@
       <c r="C62" s="4">
         <v>9.31</v>
       </c>
-      <c r="D62" s="9">
+      <c r="D62" s="6">
         <f t="shared" si="1"/>
         <v>0.15413907284768213</v>
       </c>
@@ -1914,7 +1903,7 @@
       <c r="C63" s="4">
         <v>8.73</v>
       </c>
-      <c r="D63" s="9">
+      <c r="D63" s="6">
         <f t="shared" si="1"/>
         <v>0.14405940594059408</v>
       </c>
@@ -1937,7 +1926,7 @@
       <c r="C64" s="4">
         <v>13.03</v>
       </c>
-      <c r="D64" s="9">
+      <c r="D64" s="6">
         <f t="shared" si="1"/>
         <v>0.2143092105263158</v>
       </c>
@@ -1960,7 +1949,7 @@
       <c r="C65" s="4">
         <v>11.5</v>
       </c>
-      <c r="D65" s="9">
+      <c r="D65" s="6">
         <f t="shared" si="1"/>
         <v>0.18852459016393441</v>
       </c>
@@ -1983,7 +1972,7 @@
       <c r="C66" s="4">
         <v>17.09</v>
       </c>
-      <c r="D66" s="9">
+      <c r="D66" s="6">
         <f t="shared" si="1"/>
         <v>0.27833876221498371</v>
       </c>
@@ -2006,7 +1995,7 @@
       <c r="C67" s="4">
         <v>21.62</v>
       </c>
-      <c r="D67" s="9">
+      <c r="D67" s="6">
         <f t="shared" ref="D67:D130" si="4">C67/B67</f>
         <v>0.34983818770226538</v>
       </c>
@@ -2029,7 +2018,7 @@
       <c r="C68" s="4">
         <v>13.51</v>
       </c>
-      <c r="D68" s="9">
+      <c r="D68" s="6">
         <f t="shared" si="4"/>
         <v>0.21720257234726686</v>
       </c>
@@ -2052,7 +2041,7 @@
       <c r="C69" s="4">
         <v>15.6</v>
       </c>
-      <c r="D69" s="9">
+      <c r="D69" s="6">
         <f t="shared" si="4"/>
         <v>0.24920127795527156</v>
       </c>
@@ -2075,7 +2064,7 @@
       <c r="C70" s="4">
         <v>16.38</v>
       </c>
-      <c r="D70" s="9">
+      <c r="D70" s="6">
         <f t="shared" si="4"/>
         <v>0.26</v>
       </c>
@@ -2098,7 +2087,7 @@
       <c r="C71" s="4">
         <v>13.9</v>
       </c>
-      <c r="D71" s="9">
+      <c r="D71" s="6">
         <f t="shared" si="4"/>
         <v>0.2231139646869984</v>
       </c>
@@ -2121,7 +2110,7 @@
       <c r="C72" s="4">
         <v>10.1</v>
       </c>
-      <c r="D72" s="9">
+      <c r="D72" s="6">
         <f t="shared" si="4"/>
         <v>0.16369529983792544</v>
       </c>
@@ -2144,7 +2133,7 @@
       <c r="C73" s="4">
         <v>10.15</v>
       </c>
-      <c r="D73" s="9">
+      <c r="D73" s="6">
         <f t="shared" si="4"/>
         <v>0.16639344262295083</v>
       </c>
@@ -2167,7 +2156,7 @@
       <c r="C74" s="4">
         <v>11.05</v>
       </c>
-      <c r="D74" s="9">
+      <c r="D74" s="6">
         <f t="shared" si="4"/>
         <v>0.17967479674796749</v>
       </c>
@@ -2190,7 +2179,7 @@
       <c r="C75" s="4">
         <v>11.96</v>
       </c>
-      <c r="D75" s="9">
+      <c r="D75" s="6">
         <f t="shared" si="4"/>
         <v>0.19290322580645164</v>
       </c>
@@ -2213,7 +2202,7 @@
       <c r="C76" s="4">
         <v>15.62</v>
       </c>
-      <c r="D76" s="9">
+      <c r="D76" s="6">
         <f t="shared" si="4"/>
         <v>0.24872611464968153</v>
       </c>
@@ -2236,7 +2225,7 @@
       <c r="C77" s="4">
         <v>11.47</v>
       </c>
-      <c r="D77" s="9">
+      <c r="D77" s="6">
         <f t="shared" si="4"/>
         <v>0.18034591194968555</v>
       </c>
@@ -2259,7 +2248,7 @@
       <c r="C78" s="4">
         <v>10.42</v>
       </c>
-      <c r="D78" s="9">
+      <c r="D78" s="6">
         <f t="shared" si="4"/>
         <v>0.16180124223602482</v>
       </c>
@@ -2282,7 +2271,7 @@
       <c r="C79" s="4">
         <v>10.25</v>
       </c>
-      <c r="D79" s="9">
+      <c r="D79" s="6">
         <f t="shared" si="4"/>
         <v>0.1572085889570552</v>
       </c>
@@ -2305,7 +2294,7 @@
       <c r="C80" s="4">
         <v>10.75</v>
       </c>
-      <c r="D80" s="9">
+      <c r="D80" s="6">
         <f t="shared" si="4"/>
         <v>0.16287878787878787</v>
       </c>
@@ -2328,7 +2317,7 @@
       <c r="C81" s="4">
         <v>11.9</v>
       </c>
-      <c r="D81" s="9">
+      <c r="D81" s="6">
         <f t="shared" si="4"/>
         <v>0.1792168674698795</v>
       </c>
@@ -2351,7 +2340,7 @@
       <c r="C82" s="4">
         <v>12.53</v>
       </c>
-      <c r="D82" s="9">
+      <c r="D82" s="6">
         <f t="shared" si="4"/>
         <v>0.18757485029940119</v>
       </c>
@@ -2374,7 +2363,7 @@
       <c r="C83" s="4">
         <v>13.01</v>
       </c>
-      <c r="D83" s="9">
+      <c r="D83" s="6">
         <f t="shared" si="4"/>
         <v>0.19360119047619045</v>
       </c>
@@ -2397,7 +2386,7 @@
       <c r="C84" s="4">
         <v>12</v>
       </c>
-      <c r="D84" s="9">
+      <c r="D84" s="6">
         <f t="shared" si="4"/>
         <v>0.1775147928994083</v>
       </c>
@@ -2420,7 +2409,7 @@
       <c r="C85" s="4">
         <v>15.99</v>
       </c>
-      <c r="D85" s="9">
+      <c r="D85" s="6">
         <f t="shared" si="4"/>
         <v>0.2351470588235294</v>
       </c>
@@ -2443,7 +2432,7 @@
       <c r="C86" s="4">
         <v>18.29</v>
       </c>
-      <c r="D86" s="9">
+      <c r="D86" s="6">
         <f t="shared" si="4"/>
         <v>0.26739766081871341</v>
       </c>
@@ -2466,7 +2455,7 @@
       <c r="C87" s="4">
         <v>16.72</v>
       </c>
-      <c r="D87" s="9">
+      <c r="D87" s="6">
         <f t="shared" si="4"/>
         <v>0.24302325581395348</v>
       </c>
@@ -2489,7 +2478,7 @@
       <c r="C88" s="4">
         <v>13.79</v>
       </c>
-      <c r="D88" s="9">
+      <c r="D88" s="6">
         <f t="shared" si="4"/>
         <v>0.19927745664739882</v>
       </c>
@@ -2512,7 +2501,7 @@
       <c r="C89" s="4">
         <v>17.98</v>
       </c>
-      <c r="D89" s="9">
+      <c r="D89" s="6">
         <f t="shared" si="4"/>
         <v>0.25833333333333336</v>
       </c>
@@ -2535,7 +2524,7 @@
       <c r="C90" s="4">
         <v>18.34</v>
       </c>
-      <c r="D90" s="9">
+      <c r="D90" s="6">
         <f t="shared" si="4"/>
         <v>0.26200000000000001</v>
       </c>
@@ -2558,7 +2547,7 @@
       <c r="C91" s="4">
         <v>18.47</v>
       </c>
-      <c r="D91" s="9">
+      <c r="D91" s="6">
         <f t="shared" si="4"/>
         <v>0.26310541310541308</v>
       </c>
@@ -2581,7 +2570,7 @@
       <c r="C92" s="4">
         <v>21.2</v>
       </c>
-      <c r="D92" s="9">
+      <c r="D92" s="6">
         <f t="shared" si="4"/>
         <v>0.30113636363636359</v>
       </c>
@@ -2604,7 +2593,7 @@
       <c r="C93" s="4">
         <v>19.260000000000002</v>
       </c>
-      <c r="D93" s="9">
+      <c r="D93" s="6">
         <f t="shared" si="4"/>
         <v>0.27280453257790371</v>
       </c>
@@ -2627,7 +2616,7 @@
       <c r="C94" s="4">
         <v>21.63</v>
       </c>
-      <c r="D94" s="9">
+      <c r="D94" s="6">
         <f t="shared" si="4"/>
         <v>0.30550847457627117</v>
       </c>
@@ -2650,7 +2639,7 @@
       <c r="C95" s="4">
         <v>23.27</v>
       </c>
-      <c r="D95" s="9">
+      <c r="D95" s="6">
         <f t="shared" si="4"/>
         <v>0.32774647887323943</v>
       </c>
@@ -2673,7 +2662,7 @@
       <c r="C96" s="4">
         <v>24.06</v>
       </c>
-      <c r="D96" s="9">
+      <c r="D96" s="6">
         <f t="shared" si="4"/>
         <v>0.33839662447257385</v>
       </c>
@@ -2696,7 +2685,7 @@
       <c r="C97" s="4">
         <v>20.43</v>
       </c>
-      <c r="D97" s="9">
+      <c r="D97" s="6">
         <f t="shared" si="4"/>
         <v>0.28693820224719102</v>
       </c>
@@ -2719,7 +2708,7 @@
       <c r="C98" s="4">
         <v>21.51</v>
       </c>
-      <c r="D98" s="9">
+      <c r="D98" s="6">
         <f t="shared" si="4"/>
         <v>0.30168302945301545</v>
       </c>
@@ -2742,7 +2731,7 @@
       <c r="C99" s="4">
         <v>21.19</v>
       </c>
-      <c r="D99" s="9">
+      <c r="D99" s="6">
         <f t="shared" si="4"/>
         <v>0.29677871148459384</v>
       </c>
@@ -2765,7 +2754,7 @@
       <c r="C100" s="4">
         <v>17.09</v>
       </c>
-      <c r="D100" s="9">
+      <c r="D100" s="6">
         <f t="shared" si="4"/>
         <v>0.23902097902097902</v>
       </c>
@@ -2788,7 +2777,7 @@
       <c r="C101" s="4">
         <v>16.46</v>
       </c>
-      <c r="D101" s="9">
+      <c r="D101" s="6">
         <f t="shared" si="4"/>
         <v>0.2295676429567643</v>
       </c>
@@ -2811,7 +2800,7 @@
       <c r="C102" s="4">
         <v>17.260000000000002</v>
       </c>
-      <c r="D102" s="9">
+      <c r="D102" s="6">
         <f t="shared" si="4"/>
         <v>0.24005563282336578</v>
       </c>
@@ -2834,7 +2823,7 @@
       <c r="C103" s="4">
         <v>18.71</v>
       </c>
-      <c r="D103" s="9">
+      <c r="D103" s="6">
         <f t="shared" si="4"/>
         <v>0.25950069348127602</v>
       </c>
@@ -2857,7 +2846,7 @@
       <c r="C104" s="4">
         <v>13.53</v>
       </c>
-      <c r="D104" s="9">
+      <c r="D104" s="6">
         <f t="shared" si="4"/>
         <v>0.18713692946058091</v>
       </c>
@@ -2880,7 +2869,7 @@
       <c r="C105" s="4">
         <v>8.92</v>
       </c>
-      <c r="D105" s="9">
+      <c r="D105" s="6">
         <f t="shared" si="4"/>
         <v>0.12303448275862069</v>
       </c>
@@ -2903,7 +2892,7 @@
       <c r="C106" s="4">
         <v>11.19</v>
       </c>
-      <c r="D106" s="9">
+      <c r="D106" s="6">
         <f t="shared" si="4"/>
         <v>0.15370879120879122</v>
       </c>
@@ -2926,7 +2915,7 @@
       <c r="C107" s="4">
         <v>11.44</v>
       </c>
-      <c r="D107" s="9">
+      <c r="D107" s="6">
         <f t="shared" si="4"/>
         <v>0.15649794801641587</v>
       </c>
@@ -2949,7 +2938,7 @@
       <c r="C108" s="4">
         <v>9.24</v>
       </c>
-      <c r="D108" s="9">
+      <c r="D108" s="6">
         <f t="shared" si="4"/>
         <v>0.12588555858310627</v>
       </c>
@@ -2972,7 +2961,7 @@
       <c r="C109" s="4">
         <v>9.26</v>
       </c>
-      <c r="D109" s="9">
+      <c r="D109" s="6">
         <f t="shared" si="4"/>
         <v>0.12564450474898237</v>
       </c>
@@ -2995,7 +2984,7 @@
       <c r="C110" s="4">
         <v>8.85</v>
       </c>
-      <c r="D110" s="9">
+      <c r="D110" s="6">
         <f t="shared" si="4"/>
         <v>0.11959459459459459</v>
       </c>
@@ -3018,7 +3007,7 @@
       <c r="C111" s="4">
         <v>9.26</v>
       </c>
-      <c r="D111" s="9">
+      <c r="D111" s="6">
         <f t="shared" si="4"/>
         <v>0.12479784366576818</v>
       </c>
@@ -3041,7 +3030,7 @@
       <c r="C112" s="4">
         <v>7.39</v>
       </c>
-      <c r="D112" s="9">
+      <c r="D112" s="6">
         <f t="shared" si="4"/>
         <v>9.9327956989247304E-2</v>
       </c>
@@ -3064,7 +3053,7 @@
       <c r="C113" s="4">
         <v>8.76</v>
       </c>
-      <c r="D113" s="9">
+      <c r="D113" s="6">
         <f t="shared" si="4"/>
         <v>0.11742627345844504</v>
       </c>
@@ -3087,7 +3076,7 @@
       <c r="C114" s="4">
         <v>9.89</v>
       </c>
-      <c r="D114" s="9">
+      <c r="D114" s="6">
         <f t="shared" si="4"/>
         <v>0.13221925133689841</v>
       </c>
@@ -3110,7 +3099,7 @@
       <c r="C115" s="4">
         <v>10</v>
       </c>
-      <c r="D115" s="9">
+      <c r="D115" s="6">
         <f t="shared" si="4"/>
         <v>0.13333333333333333</v>
       </c>
@@ -3133,7 +3122,7 @@
       <c r="C116" s="4">
         <v>11.72</v>
       </c>
-      <c r="D116" s="9">
+      <c r="D116" s="6">
         <f t="shared" si="4"/>
         <v>0.15585106382978722</v>
       </c>
@@ -3156,7 +3145,7 @@
       <c r="C117" s="4">
         <v>14.92</v>
       </c>
-      <c r="D117" s="9">
+      <c r="D117" s="6">
         <f t="shared" si="4"/>
         <v>0.19787798408488061</v>
       </c>
@@ -3179,7 +3168,7 @@
       <c r="C118" s="4">
         <v>13.9</v>
       </c>
-      <c r="D118" s="9">
+      <c r="D118" s="6">
         <f t="shared" si="4"/>
         <v>0.18386243386243389</v>
       </c>
@@ -3202,7 +3191,7 @@
       <c r="C119" s="4">
         <v>15.09</v>
       </c>
-      <c r="D119" s="9">
+      <c r="D119" s="6">
         <f t="shared" si="4"/>
         <v>0.19907651715039579</v>
       </c>
@@ -3225,7 +3214,7 @@
       <c r="C120" s="4">
         <v>17.05</v>
       </c>
-      <c r="D120" s="9">
+      <c r="D120" s="6">
         <f t="shared" si="4"/>
         <v>0.2243421052631579</v>
       </c>
@@ -3248,7 +3237,7 @@
       <c r="C121" s="4">
         <v>15.61</v>
       </c>
-      <c r="D121" s="9">
+      <c r="D121" s="6">
         <f t="shared" si="4"/>
         <v>0.2048556430446194</v>
       </c>
@@ -3271,7 +3260,7 @@
       <c r="C122" s="4">
         <v>19.77</v>
       </c>
-      <c r="D122" s="9">
+      <c r="D122" s="6">
         <f t="shared" si="4"/>
         <v>0.25876963350785337</v>
       </c>
@@ -3294,7 +3283,7 @@
       <c r="C123" s="4">
         <v>20.32</v>
       </c>
-      <c r="D123" s="9">
+      <c r="D123" s="6">
         <f t="shared" si="4"/>
         <v>0.26527415143603134</v>
       </c>
@@ -3317,7 +3306,7 @@
       <c r="C124" s="4">
         <v>21.41</v>
       </c>
-      <c r="D124" s="9">
+      <c r="D124" s="6">
         <f t="shared" si="4"/>
         <v>0.2787760416666667</v>
       </c>
@@ -3340,7 +3329,7 @@
       <c r="C125" s="4">
         <v>20.22</v>
       </c>
-      <c r="D125" s="9">
+      <c r="D125" s="6">
         <f t="shared" si="4"/>
         <v>0.26259740259740261</v>
       </c>
@@ -3363,7 +3352,7 @@
       <c r="C126" s="4">
         <v>24.76</v>
       </c>
-      <c r="D126" s="9">
+      <c r="D126" s="6">
         <f t="shared" si="4"/>
         <v>0.32072538860103628</v>
       </c>
@@ -3386,7 +3375,7 @@
       <c r="C127" s="4">
         <v>28.33</v>
       </c>
-      <c r="D127" s="9">
+      <c r="D127" s="6">
         <f t="shared" si="4"/>
         <v>0.36602067183462528</v>
       </c>
@@ -3409,7 +3398,7 @@
       <c r="C128" s="4">
         <v>32.86</v>
       </c>
-      <c r="D128" s="9">
+      <c r="D128" s="6">
         <f t="shared" si="4"/>
         <v>0.42345360824742273</v>
       </c>
@@ -3432,7 +3421,7 @@
       <c r="C129" s="4">
         <v>40.57</v>
       </c>
-      <c r="D129" s="9">
+      <c r="D129" s="6">
         <f t="shared" si="4"/>
         <v>0.52146529562982002</v>
       </c>
@@ -3455,7 +3444,7 @@
       <c r="C130" s="4">
         <v>43.77</v>
       </c>
-      <c r="D130" s="9">
+      <c r="D130" s="6">
         <f t="shared" si="4"/>
         <v>0.56115384615384623</v>
       </c>
@@ -3478,7 +3467,7 @@
       <c r="C131" s="4">
         <v>36.979999999999997</v>
       </c>
-      <c r="D131" s="9">
+      <c r="D131" s="6">
         <f t="shared" ref="D131:D155" si="7">C131/B131</f>
         <v>0.47289002557544751</v>
       </c>
@@ -3501,7 +3490,7 @@
       <c r="C132" s="4">
         <v>30.28</v>
       </c>
-      <c r="D132" s="9">
+      <c r="D132" s="6">
         <f t="shared" si="7"/>
         <v>0.38622448979591834</v>
       </c>
@@ -3524,7 +3513,7 @@
       <c r="C133" s="4">
         <v>22.9</v>
       </c>
-      <c r="D133" s="9">
+      <c r="D133" s="6">
         <f t="shared" si="7"/>
         <v>0.29134860050890588</v>
       </c>
@@ -3547,7 +3536,7 @@
       <c r="C134" s="4">
         <v>27.66</v>
       </c>
-      <c r="D134" s="9">
+      <c r="D134" s="6">
         <f t="shared" si="7"/>
         <v>0.35101522842639593</v>
       </c>
@@ -3570,7 +3559,7 @@
       <c r="C135" s="4">
         <v>26.59</v>
       </c>
-      <c r="D135" s="9">
+      <c r="D135" s="6">
         <f t="shared" si="7"/>
         <v>0.33658227848101263</v>
       </c>
@@ -3593,7 +3582,7 @@
       <c r="C136" s="4">
         <v>26.47</v>
       </c>
-      <c r="D136" s="9">
+      <c r="D136" s="6">
         <f t="shared" si="7"/>
         <v>0.33421717171717169</v>
       </c>
@@ -3616,7 +3605,7 @@
       <c r="C137" s="4">
         <v>27.21</v>
       </c>
-      <c r="D137" s="9">
+      <c r="D137" s="6">
         <f t="shared" si="7"/>
         <v>0.34269521410579346</v>
       </c>
@@ -3639,7 +3628,7 @@
       <c r="C138" s="4">
         <v>24.02</v>
       </c>
-      <c r="D138" s="9">
+      <c r="D138" s="6">
         <f t="shared" si="7"/>
         <v>0.30175879396984928</v>
       </c>
@@ -3662,7 +3651,7 @@
       <c r="C139" s="4">
         <v>15.17</v>
       </c>
-      <c r="D139" s="9">
+      <c r="D139" s="6">
         <f t="shared" si="7"/>
         <v>0.19010025062656641</v>
       </c>
@@ -3685,7 +3674,7 @@
       <c r="C140" s="4">
         <v>20.53</v>
       </c>
-      <c r="D140" s="9">
+      <c r="D140" s="6">
         <f t="shared" si="7"/>
         <v>0.25662499999999999</v>
       </c>
@@ -3708,7 +3697,7 @@
       <c r="C141" s="4">
         <v>22.98</v>
       </c>
-      <c r="D141" s="9">
+      <c r="D141" s="6">
         <f t="shared" si="7"/>
         <v>0.28653366583541146</v>
       </c>
@@ -3731,7 +3720,7 @@
       <c r="C142" s="4">
         <v>21.21</v>
       </c>
-      <c r="D142" s="9">
+      <c r="D142" s="6">
         <f t="shared" si="7"/>
         <v>0.264134495641345</v>
       </c>
@@ -3754,7 +3743,7 @@
       <c r="C143" s="4">
         <v>21.9</v>
       </c>
-      <c r="D143" s="9">
+      <c r="D143" s="6">
         <f t="shared" si="7"/>
         <v>0.27204968944099378</v>
       </c>
@@ -3777,7 +3766,7 @@
       <c r="C144" s="4">
         <v>24.86</v>
       </c>
-      <c r="D144" s="9">
+      <c r="D144" s="6">
         <f t="shared" si="7"/>
         <v>0.30843672456575683</v>
       </c>
@@ -3800,7 +3789,7 @@
       <c r="C145" s="4">
         <v>26.49</v>
       </c>
-      <c r="D145" s="9">
+      <c r="D145" s="6">
         <f t="shared" si="7"/>
         <v>0.32784653465346536</v>
       </c>
@@ -3823,7 +3812,7 @@
       <c r="C146" s="4">
         <v>24.21</v>
       </c>
-      <c r="D146" s="9">
+      <c r="D146" s="6">
         <f t="shared" si="7"/>
         <v>0.29888888888888893</v>
       </c>
@@ -3846,7 +3835,7 @@
       <c r="C147" s="4">
         <v>28.06</v>
       </c>
-      <c r="D147" s="9">
+      <c r="D147" s="6">
         <f t="shared" si="7"/>
         <v>0.34556650246305415</v>
       </c>
@@ -3869,7 +3858,7 @@
       <c r="C148" s="4">
         <v>33.31</v>
       </c>
-      <c r="D148" s="9">
+      <c r="D148" s="6">
         <f t="shared" si="7"/>
         <v>0.40971709717097177</v>
       </c>
@@ -3892,7 +3881,7 @@
       <c r="C149" s="4">
         <v>28.38</v>
       </c>
-      <c r="D149" s="9">
+      <c r="D149" s="6">
         <f t="shared" si="7"/>
         <v>0.34822085889570553</v>
       </c>
@@ -3915,7 +3904,7 @@
       <c r="C150" s="4">
         <v>30.99</v>
       </c>
-      <c r="D150" s="9">
+      <c r="D150" s="6">
         <f t="shared" si="7"/>
         <v>0.38353960396039605</v>
       </c>
@@ -3938,7 +3927,7 @@
       <c r="C151" s="4">
         <v>34.51</v>
       </c>
-      <c r="D151" s="9">
+      <c r="D151" s="6">
         <f t="shared" si="7"/>
         <v>0.42976338729763386</v>
       </c>
@@ -3961,7 +3950,7 @@
       <c r="C152" s="4">
         <v>36.94</v>
       </c>
-      <c r="D152" s="9">
+      <c r="D152" s="6">
         <f t="shared" si="7"/>
         <v>0.45717821782178214</v>
       </c>
@@ -3984,7 +3973,7 @@
       <c r="C153" s="4">
         <v>28.34</v>
       </c>
-      <c r="D153" s="9">
+      <c r="D153" s="6">
         <f t="shared" si="7"/>
         <v>0.34858548585485855</v>
       </c>
@@ -4007,7 +3996,7 @@
       <c r="C154" s="4">
         <v>31.97</v>
       </c>
-      <c r="D154" s="9">
+      <c r="D154" s="6">
         <f t="shared" si="7"/>
         <v>0.39178921568627451</v>
       </c>
@@ -4030,7 +4019,7 @@
       <c r="C155" s="4">
         <v>37.14</v>
       </c>
-      <c r="D155" s="9">
+      <c r="D155" s="6">
         <f t="shared" si="7"/>
         <v>0.45403422982885089</v>
       </c>
@@ -4053,7 +4042,7 @@
       <c r="C156" s="4">
         <v>39.65</v>
       </c>
-      <c r="D156" s="9">
+      <c r="D156" s="6">
         <f>C156/B156</f>
         <v>0.48353658536585364</v>
       </c>
@@ -4065,13 +4054,6 @@
         <f t="shared" si="9"/>
         <v>7.6533333333333333</v>
       </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C157" s="8"/>
-      <c r="D157" s="5"/>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A158" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
